--- a/R_Codes/DataSummary/Bacteria/Sample_name/Bacteria_Summary_Domain_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/Bacteria/Sample_name/Bacteria_Summary_Domain_by_Sample_name.xlsx
@@ -388,10 +388,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999996</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.274016590030279</v>
+        <v>0.274239082564216</v>
       </c>
     </row>
   </sheetData>
@@ -427,10 +427,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999997</v>
+        <v>99.9999999999996</v>
       </c>
       <c r="D2" t="n">
-        <v>0.784646550861116</v>
+        <v>0.802453890697945</v>
       </c>
     </row>
   </sheetData>
@@ -466,10 +466,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999995</v>
+        <v>99.9999999999994</v>
       </c>
       <c r="D2" t="n">
-        <v>0.189884192435042</v>
+        <v>0.190065819321978</v>
       </c>
     </row>
   </sheetData>
